--- a/output/roomself_excel/6306.xlsx
+++ b/output/roomself_excel/6306.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>499584</v>
+        <v>86130</v>
       </c>
       <c r="D2" t="n">
-        <v>7196</v>
+        <v>2348</v>
       </c>
       <c r="E2" t="n">
-        <v>1378</v>
+        <v>321</v>
       </c>
       <c r="F2" t="n">
-        <v>633</v>
+        <v>312</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>85408</v>
+        <v>477810</v>
       </c>
       <c r="D3" t="n">
-        <v>2344</v>
+        <v>6360</v>
       </c>
       <c r="E3" t="n">
-        <v>337</v>
+        <v>1045</v>
       </c>
       <c r="F3" t="n">
-        <v>303</v>
+        <v>633</v>
       </c>
     </row>
     <row r="4">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>78146</v>
+        <v>85408</v>
       </c>
       <c r="D4" t="n">
-        <v>2400</v>
+        <v>2344</v>
       </c>
       <c r="E4" t="n">
-        <v>286</v>
+        <v>337</v>
       </c>
       <c r="F4" t="n">
-        <v>23</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20085</v>
+        <v>78146</v>
       </c>
       <c r="D5" t="n">
-        <v>1276</v>
+        <v>2400</v>
       </c>
       <c r="E5" t="n">
-        <v>411</v>
+        <v>286</v>
       </c>
       <c r="F5" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>92368</v>
+        <v>99634</v>
       </c>
       <c r="D6" t="n">
-        <v>2476</v>
+        <v>2560</v>
       </c>
       <c r="E6" t="n">
-        <v>1008</v>
+        <v>396</v>
       </c>
       <c r="F6" t="n">
-        <v>314</v>
+        <v>303</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>33434</v>
+        <v>103748</v>
       </c>
       <c r="D7" t="n">
-        <v>1688</v>
+        <v>2616</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>286</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
@@ -602,16 +602,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16497</v>
+        <v>33434</v>
       </c>
       <c r="D8" t="n">
-        <v>1032</v>
+        <v>1688</v>
       </c>
       <c r="E8" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>86130</v>
+        <v>16497</v>
       </c>
       <c r="D9" t="n">
-        <v>2348</v>
+        <v>1032</v>
       </c>
       <c r="E9" t="n">
-        <v>676</v>
+        <v>117</v>
       </c>
       <c r="F9" t="n">
-        <v>312</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>99634</v>
+        <v>15428</v>
       </c>
       <c r="D10" t="n">
-        <v>2560</v>
+        <v>996</v>
       </c>
       <c r="E10" t="n">
-        <v>396</v>
+        <v>123</v>
       </c>
       <c r="F10" t="n">
-        <v>303</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>103748</v>
+        <v>39780</v>
       </c>
       <c r="D11" t="n">
-        <v>2616</v>
+        <v>1652</v>
       </c>
       <c r="E11" t="n">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="F11" t="n">
-        <v>28</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -690,16 +690,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>49485</v>
+        <v>20085</v>
       </c>
       <c r="D12" t="n">
-        <v>2092</v>
+        <v>1276</v>
       </c>
       <c r="E12" t="n">
-        <v>548</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>308</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -708,19 +708,63 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>39780</v>
+        <v>92368</v>
       </c>
       <c r="D13" t="n">
-        <v>1652</v>
+        <v>2476</v>
       </c>
       <c r="E13" t="n">
-        <v>276</v>
+        <v>251</v>
       </c>
       <c r="F13" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>21774</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1212</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>34057</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1560</v>
+      </c>
+      <c r="E15" t="n">
+        <v>248</v>
+      </c>
+      <c r="F15" t="n">
         <v>185</v>
       </c>
     </row>

--- a/output/roomself_excel/6306.xlsx
+++ b/output/roomself_excel/6306.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,77 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_5</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_5</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_5</t>
         </is>
       </c>
     </row>
@@ -475,12 +540,37 @@
       <c r="D2" t="n">
         <v>2348</v>
       </c>
-      <c r="E2" t="n">
-        <v>321</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>312</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="G2" t="n">
+        <v>22</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>278</v>
+      </c>
+      <c r="J2" t="n">
+        <v>24</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,11 +587,60 @@
       <c r="D3" t="n">
         <v>6360</v>
       </c>
-      <c r="E3" t="n">
-        <v>1045</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>633</v>
+        <v>171</v>
+      </c>
+      <c r="G3" t="n">
+        <v>33</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1128</v>
+      </c>
+      <c r="J3" t="n">
+        <v>33</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>103</v>
+      </c>
+      <c r="M3" t="n">
+        <v>34</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>280</v>
+      </c>
+      <c r="P3" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>699</v>
+      </c>
+      <c r="S3" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -519,12 +658,37 @@
       <c r="D4" t="n">
         <v>2344</v>
       </c>
-      <c r="E4" t="n">
-        <v>337</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>303</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="G4" t="n">
+        <v>23</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>314</v>
+      </c>
+      <c r="J4" t="n">
+        <v>31</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +705,37 @@
       <c r="D5" t="n">
         <v>2400</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>286</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>23</v>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>256</v>
+      </c>
+      <c r="J5" t="n">
+        <v>16</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +752,37 @@
       <c r="D6" t="n">
         <v>2560</v>
       </c>
-      <c r="E6" t="n">
-        <v>396</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>303</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="G6" t="n">
+        <v>31</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>272</v>
+      </c>
+      <c r="J6" t="n">
+        <v>28</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +799,45 @@
       <c r="D7" t="n">
         <v>2616</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>60</v>
+      </c>
+      <c r="G7" t="n">
+        <v>41</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>308</v>
+      </c>
+      <c r="J7" t="n">
+        <v>16</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
         <v>286</v>
       </c>
-      <c r="F7" t="n">
+      <c r="M7" t="n">
         <v>28</v>
       </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +854,29 @@
       <c r="D8" t="n">
         <v>1688</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="G8" t="n">
+        <v>16</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +893,29 @@
       <c r="D9" t="n">
         <v>1032</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>117</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>33</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +932,29 @@
       <c r="D10" t="n">
         <v>996</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>123</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>24</v>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +971,37 @@
       <c r="D11" t="n">
         <v>1652</v>
       </c>
-      <c r="E11" t="n">
-        <v>276</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>185</v>
-      </c>
+        <v>520</v>
+      </c>
+      <c r="G11" t="n">
+        <v>16</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>153</v>
+      </c>
+      <c r="J11" t="n">
+        <v>16</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +1018,29 @@
       <c r="D12" t="n">
         <v>1276</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="G12" t="n">
+        <v>16</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +1057,29 @@
       <c r="D13" t="n">
         <v>2476</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>251</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>31</v>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +1096,21 @@
       <c r="D14" t="n">
         <v>1212</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +1127,37 @@
       <c r="D15" t="n">
         <v>1560</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>248</v>
       </c>
-      <c r="F15" t="n">
-        <v>185</v>
-      </c>
+      <c r="G15" t="n">
+        <v>33</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>55</v>
+      </c>
+      <c r="J15" t="n">
+        <v>24</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/6306.xlsx
+++ b/output/roomself_excel/6306.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:AU15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,6 +522,146 @@
       <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ExtWallWidth_5</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_3</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_3</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_3</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_3</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_4</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_4</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_4</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_4</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_5</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_5</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_5</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_5</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_6</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_6</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_6</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_6</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_7</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_7</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_7</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_7</t>
         </is>
       </c>
     </row>
@@ -571,6 +711,46 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>242</v>
+      </c>
+      <c r="W2" t="n">
+        <v>24</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -641,6 +821,118 @@
       </c>
       <c r="S3" t="n">
         <v>22</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>65</v>
+      </c>
+      <c r="W3" t="n">
+        <v>33</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Z3" t="n">
+        <v>89</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>33</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>39</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>33</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AL3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AP3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AT3" t="n">
+        <v>274</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="4">
@@ -689,6 +981,46 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>223</v>
+      </c>
+      <c r="W4" t="n">
+        <v>23</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -736,6 +1068,46 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>242</v>
+      </c>
+      <c r="W5" t="n">
+        <v>23</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -783,6 +1155,46 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>225</v>
+      </c>
+      <c r="W6" t="n">
+        <v>28</v>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -838,6 +1250,46 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>241</v>
+      </c>
+      <c r="W7" t="n">
+        <v>28</v>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -877,6 +1329,34 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -916,6 +1396,34 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -955,6 +1463,58 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>88</v>
+      </c>
+      <c r="W10" t="n">
+        <v>24</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Z10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1002,6 +1562,58 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>80</v>
+      </c>
+      <c r="W11" t="n">
+        <v>16</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Z11" t="n">
+        <v>92</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1041,6 +1653,34 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1080,6 +1720,46 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>200</v>
+      </c>
+      <c r="W13" t="n">
+        <v>31</v>
+      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1111,6 +1791,34 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1158,6 +1866,34 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
